--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -666,43 +666,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 65637억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 65636억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 64655억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 65475억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 64668억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 64648억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 63916억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 63896억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 63012억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 62993억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 62370억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 62351억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 61037억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 61017억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -918,31 +918,31 @@
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1150억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1151억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1227억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1228억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1304억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1305억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1358억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1359억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1434억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1435억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1833,43 +1833,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 65637억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 65636억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 64655억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 65475억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 64668억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 64648억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 63916억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 63896억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 63012억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 62993억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 62370억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 62351억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 61037억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 61017억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2300,31 +2300,31 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1150억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1151억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1227억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1228억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1304억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1305억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1358억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1359억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1434억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1435억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6548,29 +6548,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.308111</v>
+        <v>-0.308119</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.315619</v>
+        <v>-0.315626</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.02106</v>
+        <v>0.034005</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>-0.0195</v>
+        <v>-0.019799</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.033243</v>
+        <v>-0.033531</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.03999</v>
+        <v>-0.040279</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.035347</v>
+        <v>-0.047725</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.056143</v>
+        <v>-0.05616</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6697,32 +6697,32 @@
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
+        <v>0.097953</v>
+      </c>
+      <c r="AG22" s="24" t="n">
         <v>0.09796299999999999</v>
-      </c>
-      <c r="AG22" s="24" t="n">
-        <v>0.09796199999999999</v>
       </c>
       <c r="AH22" s="24" t="n">
         <v>0.097959</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.09796299999999999</v>
+        <v>0.097959</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
+        <v>0.097959</v>
+      </c>
+      <c r="AL22" s="24" t="n">
+        <v>0.09796100000000001</v>
+      </c>
+      <c r="AM22" s="24" t="n">
         <v>0.09796299999999999</v>
       </c>
-      <c r="AL22" s="24" t="n">
-        <v>0.097953</v>
-      </c>
-      <c r="AM22" s="24" t="n">
-        <v>0.097955</v>
-      </c>
       <c r="AN22" s="24" t="n">
-        <v>0.097954</v>
+        <v>0.09796199999999999</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6852,32 +6852,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
+        <v>0.089253</v>
+      </c>
+      <c r="AG23" s="24" t="n">
+        <v>0.089255</v>
+      </c>
+      <c r="AH23" s="24" t="n">
         <v>0.089252</v>
       </c>
-      <c r="AG23" s="24" t="n">
-        <v>0.089254</v>
-      </c>
-      <c r="AH23" s="24" t="n">
-        <v>0.089255</v>
-      </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08926000000000001</v>
+        <v>0.089253</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08926000000000001</v>
+        <v>0.089254</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089254</v>
+        <v>0.089258</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08926000000000001</v>
+        <v>0.089253</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.08926000000000001</v>
+        <v>0.089253</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7142,16 +7142,16 @@
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>8.81</v>
+        <v>8.82</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>9.359999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>9.75</v>
+        <v>9.76</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>10.29</v>
+        <v>10.3</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7442,26 +7442,26 @@
         <v>0.119447</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.119511</v>
+        <v>0.119517</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.119432</v>
+        <v>0.119446</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.119466</v>
+        <v>0.119494</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.119431</v>
+        <v>0.119458</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.119507</v>
+        <v>0.119419</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.11951</v>
+        <v>0.119421</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7597,26 +7597,26 @@
         <v>0.941771</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.941885</v>
+        <v>0.941778</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.941743</v>
+        <v>0.941735</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.94176</v>
+        <v>0.9417450000000001</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.941779</v>
+        <v>0.941764</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.941774</v>
+        <v>0.941767</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.941703</v>
+        <v>0.941822</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -7859,23 +7859,23 @@
         <v>21.45</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AL30" s="29" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="AM30" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AN30" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AL30" s="29" t="n">
-        <v>21.46</v>
-      </c>
-      <c r="AM30" s="29" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AN30" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -7981,26 +7981,26 @@
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>21.45</v>
+        <v>21.44</v>
       </c>
       <c r="AH31" s="29" t="n">
         <v>0.01</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AL31" s="29" t="n">
         <v>21.45</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN31" s="29" t="n">
         <v>0</v>
@@ -8243,23 +8243,23 @@
         <v>0.248904</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.273596</v>
+        <v>0.276747</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.216199</v>
+        <v>0.21561</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.177004</v>
+        <v>0.176629</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.107314</v>
+        <v>0.107116</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.134338</v>
+        <v>0.134103</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.116943</v>
+        <v>0.116762</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8371,23 +8371,23 @@
         <v>0.054665</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.071154</v>
+        <v>0.071973</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.066853</v>
+        <v>0.066785</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.062395</v>
+        <v>0.062343</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.04191</v>
+        <v>0.041875</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.055757</v>
+        <v>0.055708</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.05215</v>
+        <v>0.052106</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9029,23 +9029,23 @@
         <v>-0.612403</v>
       </c>
       <c r="AH40" s="24" t="n">
-        <v>-0.236504</v>
+        <v>-0.239075</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>-0.18232</v>
+        <v>-0.185083</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>-0.15864</v>
+        <v>-0.161473</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.006667</v>
+        <v>-0.01</v>
       </c>
       <c r="AM40" s="24" t="n">
-        <v>0.003367</v>
+        <v>0.006757</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>0.013514</v>
+        <v>0.020339</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -9446,32 +9446,32 @@
         <v/>
       </c>
       <c r="AF43" s="24" t="n">
+        <v>0.089253</v>
+      </c>
+      <c r="AG43" s="24" t="n">
+        <v>0.089255</v>
+      </c>
+      <c r="AH43" s="24" t="n">
         <v>0.089252</v>
       </c>
-      <c r="AG43" s="24" t="n">
-        <v>0.089254</v>
-      </c>
-      <c r="AH43" s="24" t="n">
-        <v>0.089255</v>
-      </c>
       <c r="AI43" s="24" t="n">
-        <v>0.08926000000000001</v>
+        <v>0.089253</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.08926000000000001</v>
+        <v>0.089254</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.089254</v>
+        <v>0.089258</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>0.08926000000000001</v>
+        <v>0.089253</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>0.08926000000000001</v>
+        <v>0.089253</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -660,49 +660,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66113억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 67102억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 65636억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 69348억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 65475억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 73275억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 64648억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 77533억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 63896억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 82494억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 62993억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 87565억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 62351억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 92791억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 61017억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 96850억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -906,43 +906,43 @@
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1018억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1019억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1074억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1079억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1151억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1165억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1228억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1256억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1305억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1352억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1359억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1434억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1435억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1543억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1827,49 +1827,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66113억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 67102억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 65636억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 69348억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 65475억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 73275억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 64648억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 77533억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 63896억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 82494억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 62993억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 87565억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 62351억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 92791억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 61017억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 96850억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2288,43 +2288,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1018억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1019억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1074억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1079억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1151억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1165억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1228억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1256억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1305억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1352억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1359억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1434억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1435억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1543억 × 2.87% − 총차입금 665억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4365,7 +4365,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 62.3, "op_wape_pct": 35.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 348.44, "rev_act": 294.69, "op_pred": 34.47, "op_act": 34.11}, {"q": "2025Q4", "rev_pred": 345.4, "rev_act": 330.21, "op_pred": 34.17, "op_act": 15.02}, {"q": "2026Q1", "rev_pred": 307.05, "rev_act": 1309.1, "op_pred": 30.38, "op_act": 56.09}, {"q": "2026Q2", "rev_pred": 361.15, "rev_act": 1313.93, "op_pred": 35.73, "op_act": 31.76}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 62.3, "op_wape_pct": 35.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 13.4, "wape_trend": 19.9, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 348.44, "rev_act": 294.69, "op_pred": 34.47, "op_act": 34.11}, {"q": "2025Q4", "rev_pred": 345.4, "rev_act": 330.21, "op_pred": 34.17, "op_act": 15.02}, {"q": "2026Q1", "rev_pred": 307.05, "rev_act": 1309.1, "op_pred": 30.38, "op_act": 56.09}, {"q": "2026Q2", "rev_pred": 361.15, "rev_act": 1313.93, "op_pred": 35.73, "op_act": 31.76}]}</t>
         </is>
       </c>
     </row>
@@ -6548,29 +6548,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.308119</v>
+        <v>-0.297761</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.315626</v>
+        <v>-0.276926</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.034005</v>
+        <v>0.157186</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>-0.019799</v>
+        <v>0.175559</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.033531</v>
+        <v>0.229381</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.040279</v>
+        <v>0.262696</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.047725</v>
+        <v>0.266339</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.05616</v>
+        <v>0.249153</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6697,16 +6697,16 @@
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.097953</v>
+        <v>0.097955</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.09796299999999999</v>
+        <v>0.09796100000000001</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.097959</v>
+        <v>0.09796100000000001</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.097959</v>
+        <v>0.097957</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
@@ -6716,13 +6716,13 @@
         <v>0.097959</v>
       </c>
       <c r="AL22" s="24" t="n">
+        <v>0.097954</v>
+      </c>
+      <c r="AM22" s="24" t="n">
+        <v>0.097959</v>
+      </c>
+      <c r="AN22" s="24" t="n">
         <v>0.09796100000000001</v>
-      </c>
-      <c r="AM22" s="24" t="n">
-        <v>0.09796299999999999</v>
-      </c>
-      <c r="AN22" s="24" t="n">
-        <v>0.09796199999999999</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6855,29 +6855,29 @@
         <v>0.089253</v>
       </c>
       <c r="AG23" s="24" t="n">
+        <v>0.089257</v>
+      </c>
+      <c r="AH23" s="24" t="n">
         <v>0.089255</v>
       </c>
-      <c r="AH23" s="24" t="n">
-        <v>0.089252</v>
-      </c>
       <c r="AI23" s="24" t="n">
-        <v>0.089253</v>
+        <v>0.089258</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.089254</v>
+        <v>0.08926099999999999</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089258</v>
+        <v>0.08925900000000001</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.089253</v>
+        <v>0.08925900000000001</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.089253</v>
+        <v>0.089257</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7129,29 +7129,29 @@
         <v>6.76</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>7.31</v>
+        <v>7.32</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>7.71</v>
+        <v>7.75</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>8.26</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>8.82</v>
+        <v>9.01</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>9.369999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>9.76</v>
+        <v>10.29</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>10.3</v>
+        <v>11.07</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7436,32 +7436,32 @@
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.119521</v>
+        <v>0.119469</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.119447</v>
+        <v>0.119518</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.119517</v>
+        <v>0.119466</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.119446</v>
+        <v>0.119511</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.119494</v>
+        <v>0.119483</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.119458</v>
+        <v>0.119455</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.119419</v>
+        <v>0.119505</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.119421</v>
+        <v>0.119459</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7591,32 +7591,32 @@
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
+        <v>0.941816</v>
+      </c>
+      <c r="AG28" s="24" t="n">
+        <v>0.9418069999999999</v>
+      </c>
+      <c r="AH28" s="24" t="n">
         <v>0.941787</v>
       </c>
-      <c r="AG28" s="24" t="n">
-        <v>0.941771</v>
-      </c>
-      <c r="AH28" s="24" t="n">
-        <v>0.941778</v>
-      </c>
       <c r="AI28" s="24" t="n">
-        <v>0.941735</v>
+        <v>0.941876</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.9417450000000001</v>
+        <v>0.941815</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.941764</v>
+        <v>0.941846</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.941767</v>
+        <v>0.941819</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.941822</v>
+        <v>0.9418570000000001</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AG30" s="29" t="n">
         <v>21.45</v>
@@ -7862,17 +7862,17 @@
         <v>-0</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL30" s="29" t="n">
         <v>21.45</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AN30" s="29" t="n">
         <v>0</v>
@@ -7984,26 +7984,26 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>21.44</v>
+        <v>21.45</v>
       </c>
       <c r="AH31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AI31" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
         <v>21.45</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -8237,29 +8237,29 @@
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.526521</v>
+        <v>0.533825</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.248904</v>
+        <v>0.265521</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.276747</v>
+        <v>0.301459</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.21561</v>
+        <v>0.245467</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.176629</v>
+        <v>0.209933</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.107116</v>
+        <v>0.145929</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.134103</v>
+        <v>0.170519</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.116762</v>
+        <v>0.152456</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8365,29 +8365,29 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.081959</v>
+        <v>0.083096</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.054665</v>
+        <v>0.058532</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.071973</v>
+        <v>0.079448</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.066785</v>
+        <v>0.077997</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.062343</v>
+        <v>0.077069</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.041875</v>
+        <v>0.060181</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.055708</v>
+        <v>0.07600899999999999</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.052106</v>
+        <v>0.07392700000000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9023,29 +9023,29 @@
       </c>
       <c r="AE40" s="25" t="n"/>
       <c r="AF40" s="24" t="n">
-        <v>-0.652901</v>
+        <v>-0.654867</v>
       </c>
       <c r="AG40" s="24" t="n">
-        <v>-0.612403</v>
+        <v>-0.6188630000000001</v>
       </c>
       <c r="AH40" s="24" t="n">
-        <v>-0.239075</v>
+        <v>-0.272494</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>-0.185083</v>
+        <v>-0.251381</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>-0.161473</v>
+        <v>-0.267806</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.01</v>
+        <v>-0.179661</v>
       </c>
       <c r="AM40" s="24" t="n">
-        <v>0.006757</v>
+        <v>-0.194346</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>0.020339</v>
+        <v>-0.202952</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -9148,23 +9148,23 @@
         <v>-0.517007</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>-0.211765</v>
+        <v>-0.223529</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>-0.202532</v>
+        <v>-0.21519</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.189189</v>
+        <v>-0.216216</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.183099</v>
+        <v>-0.211268</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.179104</v>
+        <v>-0.212121</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.15873</v>
+        <v>-0.209677</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9449,29 +9449,29 @@
         <v>0.089253</v>
       </c>
       <c r="AG43" s="24" t="n">
+        <v>0.089257</v>
+      </c>
+      <c r="AH43" s="24" t="n">
         <v>0.089255</v>
       </c>
-      <c r="AH43" s="24" t="n">
-        <v>0.089252</v>
-      </c>
       <c r="AI43" s="24" t="n">
-        <v>0.089253</v>
+        <v>0.089258</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.089254</v>
+        <v>0.08926099999999999</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.089258</v>
+        <v>0.08925900000000001</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>0.089253</v>
+        <v>0.08925900000000001</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>0.089253</v>
+        <v>0.089257</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39514,7 +39514,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2201.7</v>
+        <v>2238.4</v>
       </c>
     </row>
     <row r="30">
@@ -39534,7 +39534,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="32">
@@ -39554,7 +39554,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3033</v>
+        <v>0.3084</v>
       </c>
     </row>
     <row r="34">
@@ -39564,7 +39564,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.37</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="35">
@@ -39574,7 +39574,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>24500</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66101억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66085억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68341억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68322억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72257억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72239억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76505억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76487억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 81467억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 81450억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 86550억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 86534억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91777억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91761억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95826억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95812억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1716,49 +1716,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66101억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66085억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68341억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68322억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72257억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72239억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76505억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76487억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 81467억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 81450억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 86550억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 86534억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91777억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91761억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95826억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95812억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2112,7 +2112,7 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1269억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1268억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2172,7 +2172,7 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1269억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1268억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5240,35 +5240,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5359,35 +5359,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5478,35 +5478,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5597,35 +5597,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5716,35 +5716,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5835,35 +5835,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5954,35 +5954,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6073,35 +6073,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>6800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7180</v>
+        <v>7170</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6481,7 +6481,7 @@
         <v>6596.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7070</v>
+        <v>7103.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6640,29 +6640,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.308241247</v>
+        <v>-0.308401663</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.287428498</v>
+        <v>-0.287618767</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.141105002</v>
+        <v>0.140816821</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.169896194</v>
+        <v>0.169628307</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.232469798</v>
+        <v>0.232501629</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.266450917</v>
+        <v>0.266554133</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.270143042</v>
+        <v>0.2702517</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252559369</v>
+        <v>0.25266493</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6954,32 +6954,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.089257713</v>
+        <v>0.089256326</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.08925843999999999</v>
+        <v>0.089260913</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.08925973800000001</v>
+        <v>0.089262077</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.089255899</v>
+        <v>0.08925725499999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.089257235</v>
+        <v>0.089257709</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089260715</v>
+        <v>0.089260409</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08925986599999999</v>
+        <v>0.08925886700000001</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.089258238</v>
+        <v>0.089255921</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.007846054999999999</v>
+        <v>-0.008644117999999999</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.00355188</v>
+        <v>0.002806338</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.001040441</v>
+        <v>0.000679294</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.446555694</v>
+        <v>21.448207959</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.005871282</v>
+        <v>-0.004338502</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.003537428</v>
+        <v>-0.004953166</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.011490513</v>
+        <v>-6.8097e-05</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.451122917</v>
+        <v>21.452465186</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.002098732</v>
+        <v>-0.000923927</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.005756806</v>
+        <v>-0.013054279</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.003573087</v>
+        <v>-0.004226773</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.006640421</v>
+        <v>0.006040866</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.002278186</v>
+        <v>-0.009390101</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.444264985</v>
+        <v>21.447094553</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.002441292</v>
+        <v>0.005166427</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.007331642</v>
+        <v>-0.004619496</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.001581136</v>
+        <v>0.004221846</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.448379837</v>
+        <v>21.450955858</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.003808525</v>
+        <v>-0.001379331</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000970784</v>
+        <v>-0.008519402000000001</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8550,29 +8550,29 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.047591895</v>
+        <v>-0.047575367</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.033761681</v>
+        <v>-0.033743742</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.05819968</v>
+        <v>-0.05818861</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.066544619</v>
+        <v>-0.06652237799999999</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.077182373</v>
+        <v>-0.077156427</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.066469638</v>
+        <v>-0.06644088099999999</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.10375043</v>
+        <v>-0.103713188</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.122243243</v>
+        <v>-0.122208995</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8678,29 +8678,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.06385975000000001</v>
+        <v>0.06383757299999999</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.040556175</v>
+        <v>0.040536174</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.064919064</v>
+        <v>0.064911648</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.065645782</v>
+        <v>0.06563005600000001</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.066694912</v>
+        <v>0.066681379</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.049698795</v>
+        <v>0.04967767</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.068969051</v>
+        <v>0.068967692</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.068140085</v>
+        <v>0.068139243</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>7180</v>
+        <v>7170</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194630703619369</v>
+        <v>0.1194745385225171</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.09795830642806809</v>
+        <v>0.09795890803149095</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9418076351583039</v>
+        <v>0.9418094516769795</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02799638787134373</v>
+        <v>0.02800363246473719</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.0343900315948308</v>
+        <v>0.03439314420315647</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39694,7 +39694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1654.3</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="30">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66085억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66071억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68322억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68300억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72239억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72216억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76487억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76466억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 81450억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 81430억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 86534억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 86515억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91761억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91743억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95812억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95795억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1716,49 +1716,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66085억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66071억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68322억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68300억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72239억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72216억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76487억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76466억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 81450억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 81430억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 86534억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 86515억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91761억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91743억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95812억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95795억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5240,35 +5240,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5359,35 +5359,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5478,35 +5478,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5597,35 +5597,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5716,35 +5716,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5835,35 +5835,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5954,35 +5954,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6073,35 +6073,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>6800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7170</v>
+        <v>7050</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6481,7 +6481,7 @@
         <v>6596.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7103.3</v>
+        <v>7085</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6640,29 +6640,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.308401663</v>
+        <v>-0.308546801</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.287618767</v>
+        <v>-0.2878547</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.140816821</v>
+        <v>0.140459476</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.169628307</v>
+        <v>0.16930461</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.232501629</v>
+        <v>0.232451004</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.266554133</v>
+        <v>0.266685191</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.2702517</v>
+        <v>0.270386917</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.25266493</v>
+        <v>0.252782604</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6954,32 +6954,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.089256326</v>
+        <v>0.089252966</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.089260913</v>
+        <v>0.089258424</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.089262077</v>
+        <v>0.089259723</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08925725499999999</v>
+        <v>0.08925332699999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.089257709</v>
+        <v>0.08925321999999999</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089260409</v>
+        <v>0.089255431</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08925886700000001</v>
+        <v>0.08926141899999999</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.089255921</v>
+        <v>0.089257004</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.008644117999999999</v>
+        <v>-0.008384302999999999</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.002806338</v>
+        <v>0.003185077</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.000679294</v>
+        <v>-0.006439327</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.448207959</v>
+        <v>21.452349741</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.004338502</v>
+        <v>-0.010277987</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.004953166</v>
+        <v>-0.000920861</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-6.8097e-05</v>
+        <v>-0.005988475</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.452465186</v>
+        <v>21.446604224</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.000923927</v>
+        <v>0.002052078</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.013054279</v>
+        <v>-0.010003789</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.004226773</v>
+        <v>-0.004018629</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.006040866</v>
+        <v>0.006359273</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009390101</v>
+        <v>-0.0055516</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.447094553</v>
+        <v>21.442700149</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.005166427</v>
+        <v>0.000692463</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.004619496</v>
+        <v>-0.009123396000000001</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.004221846</v>
+        <v>-0.000241408</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.450955858</v>
+        <v>21.446544534</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.001379331</v>
+        <v>0.002528015</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.008519402000000001</v>
+        <v>-0.004545229</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8550,29 +8550,29 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.047575367</v>
+        <v>-0.047567103</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.033743742</v>
+        <v>-0.033717419</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.05818861</v>
+        <v>-0.058159582</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.06652237799999999</v>
+        <v>-0.06649887</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.077156427</v>
+        <v>-0.077128909</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.06644088099999999</v>
+        <v>-0.066410659</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.103713188</v>
+        <v>-0.103673498</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.122208995</v>
+        <v>-0.122145077</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8678,29 +8678,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.06383757299999999</v>
+        <v>0.063826484</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.040536174</v>
+        <v>0.040505326</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.064911648</v>
+        <v>0.06488419600000001</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.06563005600000001</v>
+        <v>0.065615563</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.066681379</v>
+        <v>0.06666902099999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.04967767</v>
+        <v>0.04966564</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.068967692</v>
+        <v>0.068958992</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.068139243</v>
+        <v>0.06812465400000001</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9363,11 +9363,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>7170</v>
+        <v>7050</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,950원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,220원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194745385225171</v>
+        <v>0.1194683582540402</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.09795890803149095</v>
+        <v>0.09795801486775235</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9418094516769795</v>
+        <v>0.941808773710316</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02800363246473719</v>
+        <v>0.0280121339682964</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03439314420315647</v>
+        <v>0.03439681079456637</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39694,7 +39694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1654</v>
+        <v>1653.8</v>
       </c>
     </row>
     <row r="30">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="32">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -669,7 +669,7 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66071억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66063억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
@@ -687,25 +687,25 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76466억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76465억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 81430억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 81429억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 86515억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 86514억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91743억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91742억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
@@ -1716,7 +1716,7 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66071억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66063억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1734,25 +1734,25 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76466억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76465억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 81430억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 81429억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 86515억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 86514억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91743억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91742억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5240,35 +5240,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5359,35 +5359,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5478,35 +5478,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5597,35 +5597,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5716,35 +5716,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5835,35 +5835,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5954,35 +5954,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6073,35 +6073,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>6800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>7050</v>
+        <v>6830</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6390,7 +6390,7 @@
         <v>5160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>6700</v>
+        <v>6670</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6481,7 +6481,7 @@
         <v>6596.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7085</v>
+        <v>7032</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6640,10 +6640,10 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.308546801</v>
+        <v>-0.308638467</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.2878547</v>
+        <v>-0.287862311</v>
       </c>
       <c r="AH21" s="24" t="n">
         <v>0.140459476</v>
@@ -6653,10 +6653,10 @@
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.232451004</v>
+        <v>0.232603363</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.266685191</v>
+        <v>0.266698728</v>
       </c>
       <c r="AM21" s="24" t="n">
         <v>0.270386917</v>
@@ -6954,10 +6954,10 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.089252966</v>
+        <v>0.08925375100000001</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.089258424</v>
+        <v>0.089259378</v>
       </c>
       <c r="AH23" s="24" t="n">
         <v>0.089259723</v>
@@ -6970,13 +6970,13 @@
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08925321999999999</v>
+        <v>0.08925402</v>
       </c>
       <c r="AL23" s="24" t="n">
         <v>0.089255431</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08926141899999999</v>
+        <v>0.08925346300000001</v>
       </c>
       <c r="AN23" s="24" t="n">
         <v>0.089257004</v>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.008384302999999999</v>
+        <v>-0.008464858</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.003185077</v>
+        <v>0.003106672</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.006439327</v>
+        <v>-0.005317891</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.452349741</v>
+        <v>21.452217006</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.010277987</v>
+        <v>-0.010413655</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.000920861</v>
+        <v>-0.00105716</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.005988475</v>
+        <v>-0.006126218</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.446604224</v>
+        <v>21.446465478</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.002052078</v>
+        <v>-0.00689459</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.010003789</v>
+        <v>-0.000143212</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.004018629</v>
+        <v>-0.004139342</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.006359273</v>
+        <v>0.006238448</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.0055516</v>
+        <v>-0.013961376</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.442700149</v>
+        <v>21.452524971</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.000692463</v>
+        <v>0.000510813</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.009123396000000001</v>
+        <v>-0.009309773</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.000241408</v>
+        <v>-0.000433948</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.446544534</v>
+        <v>21.446346107</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.002528015</v>
+        <v>-0.00597078</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.004545229</v>
+        <v>-0.004753363</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8550,29 +8550,29 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.047567103</v>
+        <v>-0.047558839</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.033717419</v>
+        <v>-0.033717127</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.058159582</v>
+        <v>-0.05815906</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.06649887</v>
+        <v>-0.066498236</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.077128909</v>
+        <v>-0.07712812099999999</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.066410659</v>
+        <v>-0.066409924</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.103673498</v>
+        <v>-0.10367227</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.122145077</v>
+        <v>-0.122143462</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8678,29 +8678,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.063826484</v>
+        <v>0.063815396</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.040505326</v>
+        <v>0.040505749</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.06488419600000001</v>
+        <v>0.064884846</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.065615563</v>
+        <v>0.065616181</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.06666902099999999</v>
+        <v>0.066669609</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.04966564</v>
+        <v>0.049666051</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.068958992</v>
+        <v>0.068959536</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.06812465400000001</v>
+        <v>0.06812515700000001</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9363,11 +9363,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>7050</v>
+        <v>6830</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,220원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,110원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194683582540402</v>
+        <v>0.1194698619274773</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.09795801486775235</v>
+        <v>0.09795836821675927</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.941808773710316</v>
+        <v>0.9418079419080019</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0280121339682964</v>
+        <v>0.02801268485531185</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03439681079456637</v>
+        <v>0.03439700438168012</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39694,7 +39694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1653.8</v>
+        <v>1653.7</v>
       </c>
     </row>
     <row r="30">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="32">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -41854,7 +41854,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2279</v>
+        <v>0.2278</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 65394억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 65950억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66063억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66794억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68300억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68524억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72216억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72071억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76465억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76054억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 81429억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80843억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 86514억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85845억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91742억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91102억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95795억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95298억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1710,55 +1710,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 65394억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 65950억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66063억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66794억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68300억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68524억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72216억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72071억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76465억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76054억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 81429억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80843억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 86514억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85845억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91742억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91102억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95795억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95298억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2082,31 +2082,31 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 959억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 961억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 998억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1000억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1063억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1064억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1133억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1134억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1208억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1209억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2118,7 +2118,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1356억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1355억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2142,31 +2142,31 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 959억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 961억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 998억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1000억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1063억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1064억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1133억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1134억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1208억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1209억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2178,7 +2178,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1356억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1355억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -6636,33 +6636,33 @@
         <v>1.943788373</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>1.713144137</v>
+        <v>1.736190266</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.308638467</v>
+        <v>-0.300991981</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.287862311</v>
+        <v>-0.2855182</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.140459476</v>
+        <v>0.138177082</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.16930461</v>
+        <v>0.153213578</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.232603363</v>
+        <v>0.210344564</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.266698728</v>
+        <v>0.252764226</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.270386917</v>
+        <v>0.264052341</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252782604</v>
+        <v>0.253028005</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6947,39 +6947,39 @@
         <v>0.089255455</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.089262194</v>
+        <v>0.089262985</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.08925375100000001</v>
+        <v>0.089260931</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.089259378</v>
+        <v>0.089254138</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.089259723</v>
+        <v>0.08925641600000001</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08925332699999999</v>
+        <v>0.089256579</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08925402</v>
+        <v>0.08926007900000001</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089255431</v>
+        <v>0.089254891</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08925346300000001</v>
+        <v>0.089255669</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.089257004</v>
+        <v>0.08925535</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.008464858</v>
+        <v>-0.007477514</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.003106672</v>
+        <v>0.002582125</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.005317891</v>
+        <v>0.001302348</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.452217006</v>
+        <v>21.448689167</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.010413655</v>
+        <v>-0.008849216</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.00105716</v>
+        <v>-0.002459984</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.006126218</v>
+        <v>-0.005514607</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.446465478</v>
+        <v>21.445943602</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.00689459</v>
+        <v>-0.006892772</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.000143212</v>
+        <v>-0.005144365</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.004139342</v>
+        <v>-0.003044944</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.006238448</v>
+        <v>0.001003363</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.013961376</v>
+        <v>0.006479907</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.452524971</v>
+        <v>21.44483919</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.000510813</v>
+        <v>-0.009089801999999999</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.009309773</v>
+        <v>0.004603097</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.000433948</v>
+        <v>-0.003550329</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.446346107</v>
+        <v>21.447999227</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.00597078</v>
+        <v>-0.005551811</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.004753363</v>
+        <v>-0.007759626</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8546,33 +8546,33 @@
         <v>-0.040829623</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>-0.044600772</v>
+        <v>-0.045074493</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.047558839</v>
+        <v>-0.048235605</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.033717127</v>
+        <v>-0.033975016</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.05815906</v>
+        <v>-0.058118936</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.066498236</v>
+        <v>-0.066173382</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.07712812099999999</v>
+        <v>-0.076567596</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.066409924</v>
+        <v>-0.06565544700000001</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.10367227</v>
+        <v>-0.102820239</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.122143462</v>
+        <v>-0.121273757</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8674,33 +8674,33 @@
         <v>0.06812360000000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.066825973</v>
+        <v>0.067535755</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.063815396</v>
+        <v>0.06464839</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.040505749</v>
+        <v>0.040707357</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.064884846</v>
+        <v>0.064638403</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.065616181</v>
+        <v>0.06511038</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.066669609</v>
+        <v>0.066051631</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.049666051</v>
+        <v>0.049060975</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.068959536</v>
+        <v>0.06843059899999999</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.06812515700000001</v>
+        <v>0.067775342</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194698619274773</v>
+        <v>0.1194767845204909</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.09795836821675927</v>
+        <v>0.09795844060281238</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9418079419080019</v>
+        <v>0.9418109931668746</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02801268485531185</v>
+        <v>0.02799183297389382</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03439700438168012</v>
+        <v>0.0343854433725027</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1653.7</v>
+        <v>1665.6</v>
       </c>
     </row>
     <row r="30">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="32">
@@ -41854,7 +41854,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2278</v>
+        <v>0.2295</v>
       </c>
     </row>
     <row r="34">
@@ -41864,7 +41864,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="35">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18400</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66794억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66791억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68524억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68546억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72071억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72093억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76054억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76075억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80843억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80863억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85845억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85863억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91102억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91120억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95298억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95315억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1716,49 +1716,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66794억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66791억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68524억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68546억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72071억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72093억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76054억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76075억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80843억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80863억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85845억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85863억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91102억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91120억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95298억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95315억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2094,7 +2094,7 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1064억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1065억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2154,7 +2154,7 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1064억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1065억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -5240,35 +5240,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5359,35 +5359,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5478,35 +5478,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5597,35 +5597,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5716,35 +5716,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5835,35 +5835,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5954,35 +5954,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6073,35 +6073,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>6800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>6830</v>
+        <v>6850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6481,7 +6481,7 @@
         <v>6596.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7032</v>
+        <v>7036</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6640,29 +6640,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.300991981</v>
+        <v>-0.301014897</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.2855182</v>
+        <v>-0.285289878</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.138177082</v>
+        <v>0.138511372</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.153213578</v>
+        <v>0.153523481</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.210344564</v>
+        <v>0.210679315</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.252764226</v>
+        <v>0.252640883</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.264052341</v>
+        <v>0.26393431</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.253028005</v>
+        <v>0.252912053</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6954,32 +6954,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.089260931</v>
+        <v>0.08925292899999999</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.089254138</v>
+        <v>0.08925757099999999</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.08925641600000001</v>
+        <v>0.089260583</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.089256579</v>
+        <v>0.089261384</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08926007900000001</v>
+        <v>0.089256377</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089254891</v>
+        <v>0.089260667</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.089255669</v>
+        <v>0.089253815</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.08925535</v>
+        <v>0.089254945</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.007477514</v>
+        <v>-0.007408315</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.002582125</v>
+        <v>0.002560572</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.001302348</v>
+        <v>-0.0076178</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.448689167</v>
+        <v>21.454893199</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.008849216</v>
+        <v>-0.002590115</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.002459984</v>
+        <v>-0.006187795</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.005514607</v>
+        <v>0.002018068</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.445943602</v>
+        <v>21.442278179</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.006892772</v>
+        <v>-0.009344396</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.005144365</v>
+        <v>-0.007618312</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.003044944</v>
+        <v>-0.003850147</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.001003363</v>
+        <v>6.155699999999999e-05</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.006479907</v>
+        <v>-0.002862869</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.44483919</v>
+        <v>21.448540388</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.009089801999999999</v>
+        <v>-0.00540232</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.004603097</v>
+        <v>-0.001772751</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.003550329</v>
+        <v>0.001752801</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.447999227</v>
+        <v>21.441497645</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.005551811</v>
+        <v>-0.000425493</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.007759626</v>
+        <v>-0.012735885</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8550,29 +8550,29 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.048235605</v>
+        <v>-0.048227337</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.033975016</v>
+        <v>-0.034000782</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.058118936</v>
+        <v>-0.058137966</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.066173382</v>
+        <v>-0.066195005</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.076567596</v>
+        <v>-0.07660296699999999</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.06565544700000001</v>
+        <v>-0.065684136</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.102820239</v>
+        <v>-0.102845495</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.121273757</v>
+        <v>-0.121332611</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8681,26 +8681,26 @@
         <v>0.06464839</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.040707357</v>
+        <v>0.040728174</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.064638403</v>
+        <v>0.064657112</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.06511038</v>
+        <v>0.06513611499999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.066051631</v>
+        <v>0.06606519199999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.049060975</v>
+        <v>0.049073867</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.06843059899999999</v>
+        <v>0.06844043499999999</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.067775342</v>
+        <v>0.0677836</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9363,11 +9363,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>6830</v>
+        <v>6850</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,110원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,070원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194767845204909</v>
+        <v>0.1194778989848036</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.09795844060281238</v>
+        <v>0.09795832404172554</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9418109931668746</v>
+        <v>0.9417948497608204</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02799183297389382</v>
+        <v>0.0279845238104617</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.0343854433725027</v>
+        <v>0.03438220971235951</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66791억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66789억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68546억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68537억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72093억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72084억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76075억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76066억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80863억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80855억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85863억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85856억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91120억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91113억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95315억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95308억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1716,49 +1716,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66791억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66789억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68546억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68537억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72093억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72084억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76075억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76066억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80863억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80855억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85863억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85856억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91120억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91113억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95315억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95308억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5240,35 +5240,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5359,35 +5359,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5478,35 +5478,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5597,35 +5597,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5716,35 +5716,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5835,35 +5835,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5954,35 +5954,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6073,35 +6073,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6640,29 +6640,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.301014897</v>
+        <v>-0.301037814</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.285289878</v>
+        <v>-0.285388818</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.138511372</v>
+        <v>0.138373045</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.153523481</v>
+        <v>0.153401733</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.210679315</v>
+        <v>0.210598791</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.252640883</v>
+        <v>0.252697162</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.26393431</v>
+        <v>0.263986634</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252912053</v>
+        <v>0.252957941</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6954,32 +6954,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.08925292899999999</v>
+        <v>0.089255855</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.08925757099999999</v>
+        <v>0.089259279</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.089260583</v>
+        <v>0.089261303</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.089261384</v>
+        <v>0.08926120999999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.089256377</v>
+        <v>0.089256213</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089260667</v>
+        <v>0.089260512</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.089253815</v>
+        <v>0.089260965</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.089254945</v>
+        <v>0.089253439</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.007408315</v>
+        <v>-0.007330743</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.002560572</v>
+        <v>0.002684832</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.0076178</v>
+        <v>0.002550687</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.454893199</v>
+        <v>21.446243074</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.002590115</v>
+        <v>-0.001202619</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.006187795</v>
+        <v>-0.004803738</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.002018068</v>
+        <v>0.003342605</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.442278179</v>
+        <v>21.443670064</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.009344396</v>
+        <v>0.000849031</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.007618312</v>
+        <v>-0.006215851</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.003850147</v>
+        <v>-0.004046783</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>6.155699999999999e-05</v>
+        <v>-0.000106951</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.002862869</v>
+        <v>-0.002995979</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.448540388</v>
+        <v>21.450090733</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.00540232</v>
+        <v>-0.003836866</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.001772751</v>
+        <v>-0.000233978</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.001752801</v>
+        <v>-0.006792382</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.441497645</v>
+        <v>21.452986622</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.000425493</v>
+        <v>-0.000677417</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.012735885</v>
+        <v>-0.01129232</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8553,26 +8553,26 @@
         <v>-0.048227337</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.034000782</v>
+        <v>-0.033992095</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.058137966</v>
+        <v>-0.058128451</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.066195005</v>
+        <v>-0.066184193</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.07660296699999999</v>
+        <v>-0.07659039300000001</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.065684136</v>
+        <v>-0.06567015399999999</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.102845495</v>
+        <v>-0.102839401</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.121332611</v>
+        <v>-0.12129818</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8678,29 +8678,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.06464839</v>
+        <v>0.064637309</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.040728174</v>
+        <v>0.040728597</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.064657112</v>
+        <v>0.064647758</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.06513611499999999</v>
+        <v>0.065118551</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.06606519199999999</v>
+        <v>0.066067523</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.049073867</v>
+        <v>0.049067218</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.06844043499999999</v>
+        <v>0.068435248</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.0677836</v>
+        <v>0.067779221</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194778989848036</v>
+        <v>0.1194758349308849</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.09795832404172554</v>
+        <v>0.0979591214329419</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9417948497608204</v>
+        <v>0.9417898475994042</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0279845238104617</v>
+        <v>0.02798783232875744</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03438220971235951</v>
+        <v>0.03438364272643215</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
         <v>6800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>6850</v>
+        <v>6290</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6390,7 +6390,7 @@
         <v>5160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>6670</v>
+        <v>6250</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6481,7 +6481,7 @@
         <v>6596.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>7036</v>
+        <v>6911.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>6850</v>
+        <v>6290</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39694,7 +39694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.11</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="32">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66789억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66782억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68537억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68498억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72084억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72044억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76066억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76023억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80855억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80813억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85856억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85815억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91113억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91074억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95308억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95271억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1716,49 +1716,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66789억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66782억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68537억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68498억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72084억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72044억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76066억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76023억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80855억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80813억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85856억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85815억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91113억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91074억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95308억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95271억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2094,7 +2094,7 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1065억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1064억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2154,7 +2154,7 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1065억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1064억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5240,35 +5240,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5359,35 +5359,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5478,35 +5478,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5597,35 +5597,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5716,35 +5716,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5835,35 +5835,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5954,35 +5954,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6073,35 +6073,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>6800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>6290</v>
+        <v>6060</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6390,7 +6390,7 @@
         <v>5160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>6250</v>
+        <v>5840</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6481,7 +6481,7 @@
         <v>6596.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6911.7</v>
+        <v>6787.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6640,29 +6640,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.301037814</v>
+        <v>-0.301114202</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.285388818</v>
+        <v>-0.285784576</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.138373045</v>
+        <v>0.137739046</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.153401733</v>
+        <v>0.152737656</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.210598791</v>
+        <v>0.210097168</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.252697162</v>
+        <v>0.252805217</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.263986634</v>
+        <v>0.26414387</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252957941</v>
+        <v>0.25319008</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6954,32 +6954,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.089255855</v>
+        <v>0.089254681</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.089259279</v>
+        <v>0.089255459</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.089261303</v>
+        <v>0.089260385</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08926120999999999</v>
+        <v>0.089255024</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.089256213</v>
+        <v>0.08925781100000001</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089260512</v>
+        <v>0.089259741</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.089260965</v>
+        <v>0.08925952299999999</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.089253439</v>
+        <v>0.089257667</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.007330743</v>
+        <v>-0.005788187</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.002684832</v>
+        <v>0.004042901</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.002550687</v>
+        <v>-0.005146587</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.446243074</v>
+        <v>21.453032011</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.001202619</v>
+        <v>-0.004748142</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.004803738</v>
+        <v>-0.007598758</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.003342605</v>
+        <v>-0.001152557</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.443670064</v>
+        <v>21.448709801</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.000849031</v>
+        <v>-0.004556277</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.006215851</v>
+        <v>-0.003422424</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.004046783</v>
+        <v>-0.003215599</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.000106951</v>
+        <v>0.000513972</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.002995979</v>
+        <v>-0.000917589</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.450090733</v>
+        <v>21.438697139</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.003836866</v>
+        <v>0.004407718</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.000233978</v>
+        <v>-0.010754397</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.006792382</v>
+        <v>0.000439517</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.452986622</v>
+        <v>21.449713055</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.000677417</v>
+        <v>-0.004439602</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.01129232</v>
+        <v>-0.007391253</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8550,29 +8550,29 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.048227337</v>
+        <v>-0.048219069</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.033992095</v>
+        <v>-0.033957052</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.058128451</v>
+        <v>-0.058089868</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.066184193</v>
+        <v>-0.066130772</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.07659039300000001</v>
+        <v>-0.07653854</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.06567015399999999</v>
+        <v>-0.065601718</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.102839401</v>
+        <v>-0.102752141</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.12129818</v>
+        <v>-0.121200518</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8678,29 +8678,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.064637309</v>
+        <v>0.06462622699999999</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.040728597</v>
+        <v>0.040687387</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.064647758</v>
+        <v>0.064610984</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.065118551</v>
+        <v>0.06507708399999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.066067523</v>
+        <v>0.066040399</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.049067218</v>
+        <v>0.049033155</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.068435248</v>
+        <v>0.068408225</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.067779221</v>
+        <v>0.067763702</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9363,11 +9363,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>6290</v>
+        <v>6060</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,070원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,800원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194758349308849</v>
+        <v>0.1194528913731972</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.0979591214329419</v>
+        <v>0.09795787613015668</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9417898475994042</v>
+        <v>0.9417783191230207</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02798783232875744</v>
+        <v>0.02796533324843576</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03438364272643215</v>
+        <v>0.03437434294483063</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39694,7 +39694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1665.6</v>
+        <v>1665.3</v>
       </c>
     </row>
     <row r="30">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="32">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="33">
@@ -41854,7 +41854,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2295</v>
+        <v>0.2294</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66782억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 66780억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68498억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68536억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72044억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72081억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76023억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 76059억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80813억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80847억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85815억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85848억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91074억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 91106억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95271억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 95300억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1716,49 +1716,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66782억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 66780억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68498억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68536억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72044억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72081억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76023억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 76059억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80813억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80847억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85815억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85848억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91074억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 91106억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95271억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 95300억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2094,7 +2094,7 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1064억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1065억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2154,7 +2154,7 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1064억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1065억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5240,35 +5240,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5359,35 +5359,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5478,35 +5478,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5597,35 +5597,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5716,35 +5716,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5835,35 +5835,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5954,35 +5954,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6073,35 +6073,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>6800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>6060</v>
+        <v>6160</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6481,7 +6481,7 @@
         <v>6596.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6787.1</v>
+        <v>6725</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6640,29 +6640,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.301114202</v>
+        <v>-0.30112948</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.285784576</v>
+        <v>-0.285388818</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.137739046</v>
+        <v>0.138326936</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.152737656</v>
+        <v>0.153291054</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.210097168</v>
+        <v>0.210648275</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.252805217</v>
+        <v>0.25259066</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.26414387</v>
+        <v>0.263936568</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.25319008</v>
+        <v>0.252982217</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6954,32 +6954,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.089254681</v>
+        <v>0.089256632</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.089255459</v>
+        <v>0.089259279</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.089260385</v>
+        <v>0.089254792</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.089255024</v>
+        <v>0.08926017999999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08925781100000001</v>
+        <v>0.089255243</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089259741</v>
+        <v>0.089259599</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08925952299999999</v>
+        <v>0.08926010500000001</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.089257667</v>
+        <v>0.089260275</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.005788187</v>
+        <v>-0.007154449</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.004042901</v>
+        <v>0.0029043</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>-0.005146587</v>
+        <v>0.004002224</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.453032011</v>
+        <v>21.446480015</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.004748142</v>
+        <v>-0.009732583</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.007598758</v>
+        <v>-0.003277652</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.001152557</v>
+        <v>-0.005131811</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.448709801</v>
+        <v>21.455199958</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.004556277</v>
+        <v>0.002375413</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.003422424</v>
+        <v>-0.005877033</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.003215599</v>
+        <v>-0.004877837</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.000513972</v>
+        <v>-0.000955923</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.000917589</v>
+        <v>-0.00212545</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.438697139</v>
+        <v>21.44919361</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.004407718</v>
+        <v>-0.01306554</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.010754397</v>
+        <v>0.000503467</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.000439517</v>
+        <v>-0.006158572</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.449713055</v>
+        <v>21.4435163</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.004439602</v>
+        <v>-0.00026251</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.007391253</v>
+        <v>-0.002671376</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8553,26 +8553,26 @@
         <v>-0.048219069</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.033957052</v>
+        <v>-0.0339918</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.058089868</v>
+        <v>-0.058127928</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.066130772</v>
+        <v>-0.066174014</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.07653854</v>
+        <v>-0.076578603</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.065601718</v>
+        <v>-0.065656901</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.102752141</v>
+        <v>-0.102822676</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.121200518</v>
+        <v>-0.121290169</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8681,26 +8681,26 @@
         <v>0.06462622699999999</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.040687387</v>
+        <v>0.040729021</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.064610984</v>
+        <v>0.06464840400000001</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.06507708399999999</v>
+        <v>0.065109769</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.066040399</v>
+        <v>0.06605986799999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.049033155</v>
+        <v>0.049060163</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.068408225</v>
+        <v>0.06842951999999999</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.067763702</v>
+        <v>0.067781723</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9363,11 +9363,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>6060</v>
+        <v>6160</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,800원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,260원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194528913731972</v>
+        <v>0.1194722635655003</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.09795787613015668</v>
+        <v>0.09795861180265121</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9417783191230207</v>
+        <v>0.9417713540846</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02796533324843576</v>
+        <v>0.02799038763499492</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03437434294483063</v>
+        <v>0.03438476023790443</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39694,7 +39694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1665.3</v>
+        <v>1665.6</v>
       </c>
     </row>
     <row r="30">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="32">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="33">
@@ -41854,7 +41854,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2294</v>
+        <v>0.2295</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 66780억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 67139억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68536억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 68778억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72081억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72100억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 76059억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 75903억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80847억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80562억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85848억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85477억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 91106억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 90701억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 95300억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 94918억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1716,49 +1716,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 66780억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 67139억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68536억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 68778억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72081억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72100억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 76059억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 75903억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80847억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80562억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85848억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85477억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 91106억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 90701억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 95300억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 94918억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2088,7 +2088,7 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1000억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1001억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2118,7 +2118,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1355억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1354억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2148,7 +2148,7 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1000억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1001억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2178,7 +2178,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1355억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1354억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 11.95% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 11.95% · 근거: 최근 12분기 유효세율 11.9%(5~27% 안 — 그대로)</t>
+          <t>· 세율 11.94% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 11.95% · 근거: 최근 12분기 유효세율 11.9%(5~27% 안 — 그대로)</t>
         </is>
       </c>
     </row>
@@ -5240,35 +5240,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5359,35 +5359,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5478,35 +5478,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5597,35 +5597,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5716,35 +5716,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5835,35 +5835,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5954,35 +5954,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6073,35 +6073,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>6800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>6160</v>
+        <v>5970</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6390,7 +6390,7 @@
         <v>5160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5840</v>
+        <v>5410</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6481,7 +6481,7 @@
         <v>6596.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6725</v>
+        <v>6481.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6640,29 +6640,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.30112948</v>
+        <v>-0.297371167</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.285388818</v>
+        <v>-0.28286966</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.138326936</v>
+        <v>0.138615117</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.153291054</v>
+        <v>0.150933581</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.210648275</v>
+        <v>0.199921723</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.25259066</v>
+        <v>0.242799227</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.263936568</v>
+        <v>0.258008018</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.252982217</v>
+        <v>0.250500058</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6954,32 +6954,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.089256632</v>
+        <v>0.089257564</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.089259279</v>
+        <v>0.089253497</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.089254792</v>
+        <v>0.08925245</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08926017999999999</v>
+        <v>0.089260299</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.089255243</v>
+        <v>0.08925432599999999</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089259599</v>
+        <v>0.089253996</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08926010500000001</v>
+        <v>0.08925568</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.089260275</v>
+        <v>0.089259211</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.007154449</v>
+        <v>-0.004750784</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.0029043</v>
+        <v>0.00517938</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.004002224</v>
+        <v>0.003526157</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.446480015</v>
+        <v>21.446151769</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.009732583</v>
+        <v>-0.006254014</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.003277652</v>
+        <v>0.005277549</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.005131811</v>
+        <v>-0.008574032000000001</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.455199958</v>
+        <v>21.442910658</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.002375413</v>
+        <v>-0.007670643</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0.005877033</v>
+        <v>0.007575415</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.004877837</v>
+        <v>-0.001155312</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.000955923</v>
+        <v>0.002731201</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.00212545</v>
+        <v>0.006305607</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.44919361</v>
+        <v>21.445391035</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.01306554</v>
+        <v>-0.009204799</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.000503467</v>
+        <v>0.000330471</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.006158572</v>
+        <v>8.6411e-05</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.4435163</v>
+        <v>21.44682555</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.00026251</v>
+        <v>-0.01234944</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.002671376</v>
+        <v>0.00750923</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8550,29 +8550,29 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.048219069</v>
+        <v>-0.048541522</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.0339918</v>
+        <v>-0.034229255</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.058127928</v>
+        <v>-0.05817992</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.066174014</v>
+        <v>-0.066063513</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.076578603</v>
+        <v>-0.076311671</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.065656901</v>
+        <v>-0.06522918799999999</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.102822676</v>
+        <v>-0.102278247</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.121290169</v>
+        <v>-0.120635046</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8678,29 +8678,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.06462622699999999</v>
+        <v>0.065058399</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.040729021</v>
+        <v>0.04098301</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.06464840400000001</v>
+        <v>0.064626394</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.065109769</v>
+        <v>0.064918605</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.06605986799999999</v>
+        <v>0.065765694</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.049060163</v>
+        <v>0.04872077</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.06842951999999999</v>
+        <v>0.06809272500000001</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.067781723</v>
+        <v>0.067503102</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9363,11 +9363,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>6160</v>
+        <v>5970</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,260원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,590원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194722635655003</v>
+        <v>0.1194482340457784</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.09795861180265121</v>
+        <v>0.09795723604159012</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9417713540846</v>
+        <v>0.9417984104668177</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02799038763499492</v>
+        <v>0.02797226961571281</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03438476023790443</v>
+        <v>0.03437538861665136</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39694,7 +39694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1665.6</v>
+        <v>1670.3</v>
       </c>
     </row>
     <row r="30">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="32">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="33">
@@ -41854,7 +41854,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2295</v>
+        <v>0.2301</v>
       </c>
     </row>
     <row r="34">
@@ -41864,7 +41864,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="35">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18500</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/054540_model.xlsx
+++ b/argus/kship/models/054540_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 67139억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 67417억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 68778억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 69011억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 72100억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 72162억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 75903억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 75834억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 80562억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 80393억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 85477억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 85242억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 90701억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 90441억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−1) 94918억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
+고객 매출 가중지수(t−1) 94674억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1716,49 +1716,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 67139억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 67417억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 68778억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 69011억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 72100억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 72162억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 75903억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 75834억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 80562억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 80393억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 85477억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 85242억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 90701억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 90441억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−1) 94918억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
+        <t>추정: 고객 매출 가중지수(t−1) 94674억 × 비례계수 0.0137(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.93, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2094,13 +2094,13 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1065억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1066억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1134억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -4.70억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1135억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2154,13 +2154,13 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1065억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1066억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1134억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1135억 × 2.80%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 1982억 × 3.44%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4369,7 +4369,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 11.94% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 11.95% · 근거: 최근 12분기 유효세율 11.9%(5~27% 안 — 그대로)</t>
+          <t>· 세율 11.95% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 11.95% · 근거: 최근 12분기 유효세율 11.9%(5~27% 안 — 그대로)</t>
         </is>
       </c>
     </row>
@@ -5240,35 +5240,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5359,35 +5359,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5478,35 +5478,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5597,35 +5597,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5716,35 +5716,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5835,35 +5835,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5954,35 +5954,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6073,35 +6073,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6208,7 +6208,7 @@
         <v>6800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5970</v>
+        <v>5180</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6390,7 +6390,7 @@
         <v>5160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5410</v>
+        <v>5140</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6481,7 +6481,7 @@
         <v>6596.1</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6481.8</v>
+        <v>6167.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6640,29 +6640,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>-0.297371167</v>
+        <v>-0.294460766</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.28286966</v>
+        <v>-0.280434221</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.138615117</v>
+        <v>0.13960646</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.150933581</v>
+        <v>0.149871058</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.199921723</v>
+        <v>0.192460103</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.242799227</v>
+        <v>0.235176528</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.258008018</v>
+        <v>0.253302583</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.250500058</v>
+        <v>0.248440688</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6954,32 +6954,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.089257564</v>
+        <v>0.089257487</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.089253497</v>
+        <v>0.089258139</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.08925245</v>
+        <v>0.08925573000000001</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.089260299</v>
+        <v>0.08925615100000001</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08925432599999999</v>
+        <v>0.089260746</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.089253996</v>
+        <v>0.089261096</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08925568</v>
+        <v>0.089254584</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.089259211</v>
+        <v>0.089257766</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8159,36 +8159,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>-0.004750784</v>
+        <v>-0.007062595</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.00517938</v>
+        <v>0.002615613</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.003526157</v>
+        <v>0.000144225</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>21.446151769</v>
+        <v>21.45037274</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>-0.006254014</v>
+        <v>-0.005650602</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.005277549</v>
+        <v>-0.013706972</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.008574032000000001</v>
+        <v>0.004833971</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>21.442910658</v>
+        <v>21.44430113</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.007670643</v>
+        <v>-0.013424359</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.007575415</v>
+        <v>-0.002632907</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8287,36 +8287,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.001155312</v>
+        <v>-0.002947664</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.002731201</v>
+        <v>0.000724168</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.006305607</v>
+        <v>-0.003918686</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>21.445391035</v>
+        <v>21.455252071</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.009204799</v>
+        <v>-0.012248544</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.000330471</v>
+        <v>-0.003563882</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>8.6411e-05</v>
+        <v>0.004303604</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>21.44682555</v>
+        <v>21.443257294</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.01234944</v>
+        <v>-0.01085754</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.00750923</v>
+        <v>-0.006321898</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8550,29 +8550,29 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>-0.048541522</v>
+        <v>-0.048789562</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.034229255</v>
+        <v>-0.034455483</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.05817992</v>
+        <v>-0.058271743</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.066063513</v>
+        <v>-0.066035752</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.076311671</v>
+        <v>-0.076170396</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.06522918799999999</v>
+        <v>-0.06497894999999999</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.102278247</v>
+        <v>-0.101961017</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.120635046</v>
+        <v>-0.120266526</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8678,29 +8678,29 @@
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.065058399</v>
+        <v>0.06539083800000001</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.04098301</v>
+        <v>0.041230251</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.064626394</v>
+        <v>0.064660813</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.064918605</v>
+        <v>0.064824545</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.065765694</v>
+        <v>0.06556582599999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.04872077</v>
+        <v>0.048499132</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.06809272500000001</v>
+        <v>0.067873339</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.067503102</v>
+        <v>0.067311172</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9363,11 +9363,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>5970</v>
+        <v>5180</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,590원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,470원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1194482340457784</v>
+        <v>0.1194858052936269</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.09795723604159012</v>
+        <v>0.09795758576898472</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.9417984104668177</v>
+        <v>0.9418055495743796</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02797226961571281</v>
+        <v>0.0279624266373544</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03437538861665136</v>
+        <v>0.03437148398268128</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34561,7 +34561,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39694,7 +39694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41814,7 +41814,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1670.3</v>
+        <v>1674.2</v>
       </c>
     </row>
     <row r="30">
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.57</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="32">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="33">
@@ -41854,7 +41854,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2301</v>
+        <v>0.2307</v>
       </c>
     </row>
     <row r="34">
